--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_HS.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_HS.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Raadfa1348040432c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Ra47d770ab3884b41"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R76810c2a62474e6a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R327c574b6800429a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rb4cbf22855244580"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rc843f034a9984ed0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R75d448a65b38450b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R615a631f448a43b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rca67e09a03c549de"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R3a0b6c7c160f4834"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rbacf7bfa98d2475c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R55974312464b4700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R22c6d8f767fa4e13"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rf56a55fb28a94849"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R87650857e9da4f27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R3e0dd770c91142f4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R7c314995728c4a39"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R79fafc349df14694"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R5bc1ed95a5ac4253"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R6141b33a55314942"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="R077306b41b7448cc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Rae47948060c345b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="Red803a45d2434c69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="Re7439ef678ca45cd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R914665ff09d843fe"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R8e4d256438d64e5a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rb95537d93cf743c1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rd74def466131451f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R7c10644783604205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rcc0e1879698b4754"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R0c6a2058c24945df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="R18b14ca762884759"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="R21d6613112374cae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R7bdf2cf5a9f94cea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R3e8394e707894902"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="Rce5b9eabea9f477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R7d993fca008a42bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="R9bd5060a182f4625"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R3aa7e127a1e74523"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Rf90f30a4a7bd405a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R306ae9a54428416b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rf63efaa5e4754245"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R15ef1294c7854bb5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3489,6 +3490,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>アヤワカ</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>？？？</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
